--- a/hardware/RCKid2-ppl.xlsx
+++ b/hardware/RCKid2-ppl.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_RCKid_2024-03-09" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_RCKid_2024-06-25" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="708">
   <si>
     <t>Designator</t>
   </si>
@@ -265,7 +265,7 @@
     <t>HDR-M-2.54_1x4</t>
   </si>
   <si>
-    <t>HDR-M-2.54_1X4</t>
+    <t>hdr-m-2.54_1x4</t>
   </si>
   <si>
     <t>55.8mm</t>
@@ -856,235 +856,1249 @@
     <t>R37</t>
   </si>
   <si>
+    <t>5.4mm</t>
+  </si>
+  <si>
+    <t>-78.9mm</t>
+  </si>
+  <si>
+    <t>4.967mm</t>
+  </si>
+  <si>
+    <t>R38</t>
+  </si>
+  <si>
     <t>3.9mm</t>
   </si>
   <si>
-    <t>-80.9mm</t>
-  </si>
-  <si>
-    <t>-80.467mm</t>
-  </si>
-  <si>
-    <t>R38</t>
+    <t>-82.3mm</t>
+  </si>
+  <si>
+    <t>-82.733mm</t>
+  </si>
+  <si>
+    <t>C74</t>
+  </si>
+  <si>
+    <t>CL05A106MQ5NUNC</t>
+  </si>
+  <si>
+    <t>9.8mm</t>
+  </si>
+  <si>
+    <t>-83mm</t>
+  </si>
+  <si>
+    <t>-83.545mm</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>WMM7040DTHN0-8/TR</t>
+  </si>
+  <si>
+    <t>QFN-8_L4.0-W3.0_WMM7040DTHN0-8-TR</t>
+  </si>
+  <si>
+    <t>32.1mm</t>
+  </si>
+  <si>
+    <t>-70.6mm</t>
+  </si>
+  <si>
+    <t>31.675mm</t>
+  </si>
+  <si>
+    <t>-69.925mm</t>
+  </si>
+  <si>
+    <t>C80</t>
+  </si>
+  <si>
+    <t>28.3mm</t>
+  </si>
+  <si>
+    <t>-71.1mm</t>
+  </si>
+  <si>
+    <t>-70.555mm</t>
+  </si>
+  <si>
+    <t>C124</t>
+  </si>
+  <si>
+    <t>12mm</t>
+  </si>
+  <si>
+    <t>-86.155mm</t>
+  </si>
+  <si>
+    <t>C125</t>
+  </si>
+  <si>
+    <t>15.9mm</t>
+  </si>
+  <si>
+    <t>C126</t>
+  </si>
+  <si>
+    <t>11.3mm</t>
+  </si>
+  <si>
+    <t>C129</t>
+  </si>
+  <si>
+    <t>29.5mm</t>
+  </si>
+  <si>
+    <t>-69.7mm</t>
+  </si>
+  <si>
+    <t>-70.245mm</t>
+  </si>
+  <si>
+    <t>C130</t>
+  </si>
+  <si>
+    <t>-80.6mm</t>
+  </si>
+  <si>
+    <t>C131</t>
+  </si>
+  <si>
+    <t>-84.7mm</t>
+  </si>
+  <si>
+    <t>-85.245mm</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>HDR-M_2.54_1x4P</t>
+  </si>
+  <si>
+    <t>hdr-th_4p-p2.54-v-m</t>
+  </si>
+  <si>
+    <t>2.5mm</t>
+  </si>
+  <si>
+    <t>-70.69mm</t>
+  </si>
+  <si>
+    <t>PZ254V-11-04P</t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>0402WGF2201TCE</t>
+  </si>
+  <si>
+    <t>37mm</t>
+  </si>
+  <si>
+    <t>-54.233mm</t>
+  </si>
+  <si>
+    <t>2.2kΩ</t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t>38.2mm</t>
+  </si>
+  <si>
+    <t>R54</t>
+  </si>
+  <si>
+    <t>44.3mm</t>
+  </si>
+  <si>
+    <t>-76.6mm</t>
+  </si>
+  <si>
+    <t>44.733mm</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>1N5819WS_C191023</t>
+  </si>
+  <si>
+    <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
+  </si>
+  <si>
+    <t>21.9mm</t>
+  </si>
+  <si>
+    <t>-91.2mm</t>
+  </si>
+  <si>
+    <t>20.727mm</t>
+  </si>
+  <si>
+    <t>1N5819WS</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>AO3400A_C20917</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>6.136mm</t>
+  </si>
+  <si>
+    <t>-73.636mm</t>
+  </si>
+  <si>
+    <t>5.8mm</t>
+  </si>
+  <si>
+    <t>-73.3mm</t>
+  </si>
+  <si>
+    <t>6.002mm</t>
+  </si>
+  <si>
+    <t>-74.845mm</t>
+  </si>
+  <si>
+    <t>AO3400A</t>
+  </si>
+  <si>
+    <t>R55</t>
+  </si>
+  <si>
+    <t>-76.3mm</t>
+  </si>
+  <si>
+    <t>7.306mm</t>
+  </si>
+  <si>
+    <t>-75.994mm</t>
+  </si>
+  <si>
+    <t>R56</t>
+  </si>
+  <si>
+    <t>40.6mm</t>
+  </si>
+  <si>
+    <t>C132</t>
+  </si>
+  <si>
+    <t>CL10A226MQ8NRNC</t>
+  </si>
+  <si>
+    <t>35.2mm</t>
+  </si>
+  <si>
+    <t>-71.5mm</t>
+  </si>
+  <si>
+    <t>-70.8mm</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>76mm</t>
+  </si>
+  <si>
+    <t>-1.2mm</t>
+  </si>
+  <si>
+    <t>2.61mm</t>
+  </si>
+  <si>
+    <t>TV4</t>
+  </si>
+  <si>
+    <t>SRV05-4-P-T7_C85364</t>
+  </si>
+  <si>
+    <t>77.9mm</t>
+  </si>
+  <si>
+    <t>-7.9mm</t>
+  </si>
+  <si>
+    <t>76.55mm</t>
+  </si>
+  <si>
+    <t>-6.95mm</t>
+  </si>
+  <si>
+    <t>SRV05-4-P-T7</t>
+  </si>
+  <si>
+    <t>USB4</t>
+  </si>
+  <si>
+    <t>MC-107DM</t>
+  </si>
+  <si>
+    <t>USB-C-SMD_MC-107D</t>
+  </si>
+  <si>
+    <t>84mm</t>
+  </si>
+  <si>
+    <t>-4mm</t>
+  </si>
+  <si>
+    <t>86.308mm</t>
+  </si>
+  <si>
+    <t>0.32mm</t>
+  </si>
+  <si>
+    <t>R57</t>
+  </si>
+  <si>
+    <t>0402WGF5101TCE</t>
+  </si>
+  <si>
+    <t>79.3mm</t>
+  </si>
+  <si>
+    <t>1.4mm</t>
+  </si>
+  <si>
+    <t>78.867mm</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>R58</t>
+  </si>
+  <si>
+    <t>2.6mm</t>
+  </si>
+  <si>
+    <t>C66</t>
+  </si>
+  <si>
+    <t>CL21A476MQYNNNE</t>
+  </si>
+  <si>
+    <t>C0805</t>
+  </si>
+  <si>
+    <t>82.7mm</t>
+  </si>
+  <si>
+    <t>-88mm</t>
+  </si>
+  <si>
+    <t>83.73mm</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>C67</t>
+  </si>
+  <si>
+    <t>78mm</t>
+  </si>
+  <si>
+    <t>79.03mm</t>
+  </si>
+  <si>
+    <t>AUDIO1</t>
+  </si>
+  <si>
+    <t>PJ-3420-A-SMT</t>
+  </si>
+  <si>
+    <t>AUDIO-SMD_PJ-3420-A-SMT_C319102</t>
+  </si>
+  <si>
+    <t>82.2mm</t>
+  </si>
+  <si>
+    <t>-81.5mm</t>
+  </si>
+  <si>
+    <t>86.9mm</t>
+  </si>
+  <si>
+    <t>-78mm</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>74.5mm</t>
   </si>
   <si>
     <t>-83.5mm</t>
   </si>
   <si>
-    <t>-83.933mm</t>
-  </si>
-  <si>
-    <t>C74</t>
-  </si>
-  <si>
-    <t>CL05A106MQ5NUNC</t>
-  </si>
-  <si>
-    <t>9.8mm</t>
-  </si>
-  <si>
-    <t>-84.045mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>WMM7040DTHN0-8/TR</t>
-  </si>
-  <si>
-    <t>QFN-8_L4.0-W3.0_WMM7040DTHN0-8-TR</t>
-  </si>
-  <si>
-    <t>32.1mm</t>
-  </si>
-  <si>
-    <t>-70.6mm</t>
-  </si>
-  <si>
-    <t>31.675mm</t>
-  </si>
-  <si>
-    <t>-69.925mm</t>
-  </si>
-  <si>
-    <t>C80</t>
-  </si>
-  <si>
-    <t>28.3mm</t>
-  </si>
-  <si>
-    <t>-71.1mm</t>
-  </si>
-  <si>
-    <t>-70.555mm</t>
-  </si>
-  <si>
-    <t>C124</t>
-  </si>
-  <si>
-    <t>12mm</t>
-  </si>
-  <si>
-    <t>-86.155mm</t>
-  </si>
-  <si>
-    <t>C125</t>
-  </si>
-  <si>
-    <t>15.9mm</t>
-  </si>
-  <si>
-    <t>C126</t>
-  </si>
-  <si>
-    <t>11.3mm</t>
-  </si>
-  <si>
-    <t>R53</t>
-  </si>
-  <si>
-    <t>2.5mm</t>
-  </si>
-  <si>
-    <t>-83.067mm</t>
-  </si>
-  <si>
-    <t>C129</t>
-  </si>
-  <si>
-    <t>29.5mm</t>
-  </si>
-  <si>
-    <t>-69.7mm</t>
-  </si>
-  <si>
-    <t>-70.245mm</t>
-  </si>
-  <si>
-    <t>C130</t>
-  </si>
-  <si>
-    <t>-81.445mm</t>
-  </si>
-  <si>
-    <t>C131</t>
+    <t>-87.31mm</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>HDR-M_2.54_1x2P</t>
+  </si>
+  <si>
+    <t>SMT wire pad (2)</t>
+  </si>
+  <si>
+    <t>21.73mm</t>
+  </si>
+  <si>
+    <t>-93.7mm</t>
+  </si>
+  <si>
+    <t>23mm</t>
+  </si>
+  <si>
+    <t>B-2100S02P-A110</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>RCKid2 Cartridge Connector Female</t>
+  </si>
+  <si>
+    <t>rckid cartridge riser</t>
+  </si>
+  <si>
+    <t>75.05mm</t>
+  </si>
+  <si>
+    <t>-43mm</t>
+  </si>
+  <si>
+    <t>75.3mm</t>
+  </si>
+  <si>
+    <t>74.8mm</t>
+  </si>
+  <si>
+    <t>-17.6mm</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>ST7789V 2.8" IPS 320x240 37P 8080 8bit</t>
+  </si>
+  <si>
+    <t>ST7789V 2.8" IPS DISPLAY 320X240 37P</t>
+  </si>
+  <si>
+    <t>28.25mm</t>
+  </si>
+  <si>
+    <t>-25.1mm</t>
+  </si>
+  <si>
+    <t>-0.75mm</t>
+  </si>
+  <si>
+    <t>-49mm</t>
+  </si>
+  <si>
+    <t>-7.1mm</t>
+  </si>
+  <si>
+    <t>ST7789V 2.8&amp;quot; IPS 320x240 37P 8080 8bit</t>
+  </si>
+  <si>
+    <t>C137</t>
+  </si>
+  <si>
+    <t>22.3mm</t>
+  </si>
+  <si>
+    <t>0.7mm</t>
+  </si>
+  <si>
+    <t>21.27mm</t>
+  </si>
+  <si>
+    <t>C138</t>
+  </si>
+  <si>
+    <t>CL05A475MP5NRNC</t>
+  </si>
+  <si>
+    <t>34.7mm</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>0805W8F100KT5E</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>30.9mm</t>
+  </si>
+  <si>
+    <t>31.9mm</t>
+  </si>
+  <si>
+    <t>1Ω</t>
+  </si>
+  <si>
+    <t>C136</t>
+  </si>
+  <si>
+    <t>26.7mm</t>
+  </si>
+  <si>
+    <t>27.73mm</t>
+  </si>
+  <si>
+    <t>TF1</t>
+  </si>
+  <si>
+    <t>DM3CS-SF</t>
+  </si>
+  <si>
+    <t>TF-SMD_DM3CS-SF</t>
+  </si>
+  <si>
+    <t>31.875mm</t>
+  </si>
+  <si>
+    <t>-76.65mm</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>24.6mm</t>
+  </si>
+  <si>
+    <t>-71.4mm</t>
+  </si>
+  <si>
+    <t>23.771mm</t>
+  </si>
+  <si>
+    <t>-70.571mm</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>23.4mm</t>
+  </si>
+  <si>
+    <t>-72.6mm</t>
+  </si>
+  <si>
+    <t>22.571mm</t>
+  </si>
+  <si>
+    <t>-71.771mm</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>22.2mm</t>
+  </si>
+  <si>
+    <t>-73.8mm</t>
+  </si>
+  <si>
+    <t>21.371mm</t>
+  </si>
+  <si>
+    <t>-72.971mm</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>25.8mm</t>
+  </si>
+  <si>
+    <t>-70.2mm</t>
+  </si>
+  <si>
+    <t>24.971mm</t>
+  </si>
+  <si>
+    <t>-69.371mm</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>52mm</t>
+  </si>
+  <si>
+    <t>-54.6mm</t>
+  </si>
+  <si>
+    <t>52.829mm</t>
+  </si>
+  <si>
+    <t>-53.771mm</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>66.9mm</t>
+  </si>
+  <si>
+    <t>-62.3mm</t>
+  </si>
+  <si>
+    <t>-61.127mm</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>54.9mm</t>
+  </si>
+  <si>
+    <t>-82.5mm</t>
+  </si>
+  <si>
+    <t>53.727mm</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>26mm</t>
+  </si>
+  <si>
+    <t>-78.673mm</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>65.7mm</t>
+  </si>
+  <si>
+    <t>66.873mm</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>-72.5mm</t>
+  </si>
+  <si>
+    <t>R67</t>
+  </si>
+  <si>
+    <t>62.9mm</t>
+  </si>
+  <si>
+    <t>-81.3mm</t>
+  </si>
+  <si>
+    <t>62.467mm</t>
+  </si>
+  <si>
+    <t>R69</t>
+  </si>
+  <si>
+    <t>0402WGF2200TCE</t>
+  </si>
+  <si>
+    <t>14.6mm</t>
+  </si>
+  <si>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R70</t>
+  </si>
+  <si>
+    <t>13.3mm</t>
+  </si>
+  <si>
+    <t>R71</t>
+  </si>
+  <si>
+    <t>0603WAF1801T5E</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>-87.3mm</t>
+  </si>
+  <si>
+    <t>86.147mm</t>
+  </si>
+  <si>
+    <t>1.8kΩ</t>
+  </si>
+  <si>
+    <t>R72</t>
+  </si>
+  <si>
+    <t>-88.9mm</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>-85.5mm</t>
+  </si>
+  <si>
+    <t>25mm</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>51mm</t>
+  </si>
+  <si>
+    <t>R74</t>
+  </si>
+  <si>
+    <t>55.967mm</t>
+  </si>
+  <si>
+    <t>HOME</t>
+  </si>
+  <si>
+    <t>B3U-3000PM-B</t>
+  </si>
+  <si>
+    <t>key-smd_b3u-3000pm-b</t>
+  </si>
+  <si>
+    <t>66.8mm</t>
+  </si>
+  <si>
+    <t>-44.5mm</t>
+  </si>
+  <si>
+    <t>-46.5mm</t>
+  </si>
+  <si>
+    <t>VOL_UP</t>
+  </si>
+  <si>
+    <t>-65mm</t>
+  </si>
+  <si>
+    <t>VOL_DOWN</t>
+  </si>
+  <si>
+    <t>-75mm</t>
+  </si>
+  <si>
+    <t>-77mm</t>
+  </si>
+  <si>
+    <t>SPKR</t>
+  </si>
+  <si>
+    <t>9.3mm</t>
+  </si>
+  <si>
+    <t>-92.92mm</t>
+  </si>
+  <si>
+    <t>-91.65mm</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>58.2mm</t>
+  </si>
+  <si>
+    <t>-68.8mm</t>
+  </si>
+  <si>
+    <t>58.633mm</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>HDR-M_2.54_1x1P</t>
+  </si>
+  <si>
+    <t>hdr-th_1p-v-m_xkb_x4611wv-01i-c28d40</t>
+  </si>
+  <si>
+    <t>66.7mm</t>
+  </si>
+  <si>
+    <t>-82.1mm</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>-87.2mm</t>
+  </si>
+  <si>
+    <t>R76</t>
+  </si>
+  <si>
+    <t>39.1mm</t>
+  </si>
+  <si>
+    <t>-71.933mm</t>
+  </si>
+  <si>
+    <t>R77</t>
+  </si>
+  <si>
+    <t>35.8mm</t>
+  </si>
+  <si>
+    <t>-67.467mm</t>
+  </si>
+  <si>
+    <t>R78</t>
+  </si>
+  <si>
+    <t>36.9mm</t>
+  </si>
+  <si>
+    <t>-71.067mm</t>
+  </si>
+  <si>
+    <t>R79</t>
+  </si>
+  <si>
+    <t>38mm</t>
+  </si>
+  <si>
+    <t>R80</t>
+  </si>
+  <si>
+    <t>40.2mm</t>
+  </si>
+  <si>
+    <t>U31</t>
+  </si>
+  <si>
+    <t>ATTINY3217-MFR</t>
+  </si>
+  <si>
+    <t>WQFN-24_L4.0-W4.0-P0.50-TL-EP2.6</t>
+  </si>
+  <si>
+    <t>48.6mm</t>
+  </si>
+  <si>
+    <t>-58.6mm</t>
+  </si>
+  <si>
+    <t>47.35mm</t>
+  </si>
+  <si>
+    <t>-60.625mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>INA219AIDCNR</t>
+  </si>
+  <si>
+    <t>SOT-23-8_L3.0-W1.7-P0.65-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>55.4mm</t>
+  </si>
+  <si>
+    <t>56.626mm</t>
+  </si>
+  <si>
+    <t>-88.675mm</t>
+  </si>
+  <si>
+    <t>R81</t>
+  </si>
+  <si>
+    <t>RTT05R010FTP</t>
+  </si>
+  <si>
+    <t>58.6mm</t>
+  </si>
+  <si>
+    <t>-88.7mm</t>
+  </si>
+  <si>
+    <t>10mΩ</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>BAT60JFILM</t>
+  </si>
+  <si>
+    <t>60.6mm</t>
+  </si>
+  <si>
+    <t>-88.873mm</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>MCP73832T-2ACI/OT</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>63.1mm</t>
+  </si>
+  <si>
+    <t>-83.8mm</t>
+  </si>
+  <si>
+    <t>64.4mm</t>
+  </si>
+  <si>
+    <t>-84.75mm</t>
+  </si>
+  <si>
+    <t>C142</t>
+  </si>
+  <si>
+    <t>56.1mm</t>
   </si>
   <si>
     <t>-85.4mm</t>
   </si>
   <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>HDR-M_2.54_1x4P</t>
-  </si>
-  <si>
-    <t>HDR-TH_4P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>-70.69mm</t>
-  </si>
-  <si>
-    <t>PZ254V-11-04P</t>
-  </si>
-  <si>
-    <t>R45</t>
-  </si>
-  <si>
-    <t>0402WGF2201TCE</t>
-  </si>
-  <si>
-    <t>37mm</t>
-  </si>
-  <si>
-    <t>-54.233mm</t>
-  </si>
-  <si>
-    <t>2.2kΩ</t>
-  </si>
-  <si>
-    <t>R46</t>
-  </si>
-  <si>
-    <t>38.2mm</t>
-  </si>
-  <si>
-    <t>R54</t>
-  </si>
-  <si>
-    <t>44.3mm</t>
-  </si>
-  <si>
-    <t>-76.6mm</t>
-  </si>
-  <si>
-    <t>44.733mm</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>1N5819WS_C191023</t>
-  </si>
-  <si>
-    <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
-  </si>
-  <si>
-    <t>21.9mm</t>
-  </si>
-  <si>
-    <t>-91.2mm</t>
-  </si>
-  <si>
-    <t>23.073mm</t>
-  </si>
-  <si>
-    <t>1N5819WS</t>
-  </si>
-  <si>
-    <t>Q6</t>
-  </si>
-  <si>
-    <t>AO3400A_C20917</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>6.136mm</t>
-  </si>
-  <si>
-    <t>-73.636mm</t>
-  </si>
-  <si>
-    <t>5.8mm</t>
-  </si>
-  <si>
-    <t>-73.3mm</t>
-  </si>
-  <si>
-    <t>6.002mm</t>
-  </si>
-  <si>
-    <t>-74.845mm</t>
-  </si>
-  <si>
-    <t>AO3400A</t>
-  </si>
-  <si>
-    <t>R55</t>
-  </si>
-  <si>
-    <t>-75.3mm</t>
-  </si>
-  <si>
-    <t>7.494mm</t>
-  </si>
-  <si>
-    <t>-75.606mm</t>
-  </si>
-  <si>
-    <t>Q7</t>
+    <t>56.645mm</t>
+  </si>
+  <si>
+    <t>R83</t>
+  </si>
+  <si>
+    <t>46.4mm</t>
+  </si>
+  <si>
+    <t>-55mm</t>
+  </si>
+  <si>
+    <t>46.833mm</t>
+  </si>
+  <si>
+    <t>R84</t>
+  </si>
+  <si>
+    <t>WR04W5R11FTL</t>
+  </si>
+  <si>
+    <t>7.6mm</t>
+  </si>
+  <si>
+    <t>-56.2mm</t>
+  </si>
+  <si>
+    <t>7.906mm</t>
+  </si>
+  <si>
+    <t>-55.894mm</t>
+  </si>
+  <si>
+    <t>5.11Ω</t>
+  </si>
+  <si>
+    <t>R86</t>
+  </si>
+  <si>
+    <t>57.3mm</t>
+  </si>
+  <si>
+    <t>56.867mm</t>
+  </si>
+  <si>
+    <t>U33</t>
+  </si>
+  <si>
+    <t>SN74LVC1T45DBVR</t>
+  </si>
+  <si>
+    <t>-71.9mm</t>
+  </si>
+  <si>
+    <t>62.75mm</t>
+  </si>
+  <si>
+    <t>-72.85mm</t>
+  </si>
+  <si>
+    <t>C143</t>
+  </si>
+  <si>
+    <t>20mm</t>
+  </si>
+  <si>
+    <t>-80.2mm</t>
+  </si>
+  <si>
+    <t>-80.745mm</t>
+  </si>
+  <si>
+    <t>C144</t>
+  </si>
+  <si>
+    <t>-92.6mm</t>
+  </si>
+  <si>
+    <t>48.545mm</t>
+  </si>
+  <si>
+    <t>U34</t>
+  </si>
+  <si>
+    <t>TPS63001DRCR</t>
+  </si>
+  <si>
+    <t>VSON-10_L3.0-W3.0-P0.50-TL-EP_TPS62410DRCR</t>
+  </si>
+  <si>
+    <t>59.25mm</t>
+  </si>
+  <si>
+    <t>-76.54mm</t>
+  </si>
+  <si>
+    <t>58.25mm</t>
+  </si>
+  <si>
+    <t>-78.04mm</t>
+  </si>
+  <si>
+    <t>L13</t>
+  </si>
+  <si>
+    <t>NR3015T1R0N</t>
+  </si>
+  <si>
+    <t>IND-SMD_L3.0-W3.0_NR3010</t>
+  </si>
+  <si>
+    <t>59.3mm</t>
+  </si>
+  <si>
+    <t>-80.7mm</t>
+  </si>
+  <si>
+    <t>60.35mm</t>
+  </si>
+  <si>
+    <t>1uH</t>
+  </si>
+  <si>
+    <t>C145</t>
+  </si>
+  <si>
+    <t>CL10A106KP8NNNC</t>
+  </si>
+  <si>
+    <t>63.8mm</t>
+  </si>
+  <si>
+    <t>-77.4mm</t>
+  </si>
+  <si>
+    <t>-76.7mm</t>
+  </si>
+  <si>
+    <t>C146</t>
+  </si>
+  <si>
+    <t>51.3mm</t>
+  </si>
+  <si>
+    <t>C147</t>
+  </si>
+  <si>
+    <t>54.7mm</t>
+  </si>
+  <si>
+    <t>C148</t>
+  </si>
+  <si>
+    <t>53mm</t>
+  </si>
+  <si>
+    <t>C149</t>
+  </si>
+  <si>
+    <t>49.6mm</t>
+  </si>
+  <si>
+    <t>C150</t>
+  </si>
+  <si>
+    <t>55mm</t>
+  </si>
+  <si>
+    <t>55.7mm</t>
+  </si>
+  <si>
+    <t>C151</t>
+  </si>
+  <si>
+    <t>8.8mm</t>
+  </si>
+  <si>
+    <t>-78.8mm</t>
+  </si>
+  <si>
+    <t>-78.1mm</t>
+  </si>
+  <si>
+    <t>C152</t>
+  </si>
+  <si>
+    <t>10.6mm</t>
+  </si>
+  <si>
+    <t>LED7</t>
+  </si>
+  <si>
+    <t>XL-1615RGBC-WS2812B</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L1.6-W1.5_XL-1615RGBC-WS2812B</t>
+  </si>
+  <si>
+    <t>53.7mm</t>
+  </si>
+  <si>
+    <t>54.15mm</t>
+  </si>
+  <si>
+    <t>-69.25mm</t>
+  </si>
+  <si>
+    <t>LED8</t>
+  </si>
+  <si>
+    <t>59.75mm</t>
+  </si>
+  <si>
+    <t>-54.05mm</t>
+  </si>
+  <si>
+    <t>LED9</t>
+  </si>
+  <si>
+    <t>52.25mm</t>
+  </si>
+  <si>
+    <t>2.35mm</t>
+  </si>
+  <si>
+    <t>LED10</t>
+  </si>
+  <si>
+    <t>15.25mm</t>
+  </si>
+  <si>
+    <t>-64.95mm</t>
+  </si>
+  <si>
+    <t>LED11</t>
+  </si>
+  <si>
+    <t>21.55mm</t>
+  </si>
+  <si>
+    <t>-80.95mm</t>
+  </si>
+  <si>
+    <t>LED12</t>
+  </si>
+  <si>
+    <t>-90.7mm</t>
+  </si>
+  <si>
+    <t>48.75mm</t>
+  </si>
+  <si>
+    <t>-91.15mm</t>
+  </si>
+  <si>
+    <t>R87</t>
+  </si>
+  <si>
+    <t>0402WGF4700TCE</t>
+  </si>
+  <si>
+    <t>56.833mm</t>
+  </si>
+  <si>
+    <t>470Ω</t>
+  </si>
+  <si>
+    <t>R88</t>
+  </si>
+  <si>
+    <t>50.1mm</t>
+  </si>
+  <si>
+    <t>-91.133mm</t>
+  </si>
+  <si>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>0402WGF4701TCE</t>
+  </si>
+  <si>
+    <t>4.7kΩ</t>
+  </si>
+  <si>
+    <t>R89</t>
+  </si>
+  <si>
+    <t>-85.133mm</t>
+  </si>
+  <si>
+    <t>R91</t>
+  </si>
+  <si>
+    <t>43mm</t>
+  </si>
+  <si>
+    <t>Q9</t>
   </si>
   <si>
     <t>-79.2mm</t>
@@ -1093,994 +2107,34 @@
     <t>45.25mm</t>
   </si>
   <si>
-    <t>-78.05mm</t>
-  </si>
-  <si>
-    <t>R56</t>
-  </si>
-  <si>
-    <t>40.6mm</t>
-  </si>
-  <si>
-    <t>C132</t>
-  </si>
-  <si>
-    <t>CL10A226MQ8NRNC</t>
-  </si>
-  <si>
-    <t>35.2mm</t>
-  </si>
-  <si>
-    <t>-71.5mm</t>
-  </si>
-  <si>
-    <t>-70.8mm</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>76mm</t>
-  </si>
-  <si>
-    <t>-1.2mm</t>
-  </si>
-  <si>
-    <t>2.61mm</t>
-  </si>
-  <si>
-    <t>TV4</t>
-  </si>
-  <si>
-    <t>SRV05-4-P-T7_C85364</t>
-  </si>
-  <si>
-    <t>77.9mm</t>
-  </si>
-  <si>
-    <t>-7.9mm</t>
-  </si>
-  <si>
-    <t>76.55mm</t>
-  </si>
-  <si>
-    <t>-6.95mm</t>
-  </si>
-  <si>
-    <t>SRV05-4-P-T7</t>
-  </si>
-  <si>
-    <t>USB4</t>
-  </si>
-  <si>
-    <t>MC-107DM</t>
-  </si>
-  <si>
-    <t>USB-C-SMD_MC-107D</t>
-  </si>
-  <si>
-    <t>84mm</t>
-  </si>
-  <si>
-    <t>-4mm</t>
-  </si>
-  <si>
-    <t>86.308mm</t>
-  </si>
-  <si>
-    <t>0.32mm</t>
-  </si>
-  <si>
-    <t>R57</t>
-  </si>
-  <si>
-    <t>0402WGF5101TCE</t>
-  </si>
-  <si>
-    <t>79.3mm</t>
-  </si>
-  <si>
-    <t>1.4mm</t>
-  </si>
-  <si>
-    <t>78.867mm</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>R58</t>
-  </si>
-  <si>
-    <t>2.6mm</t>
-  </si>
-  <si>
-    <t>C66</t>
-  </si>
-  <si>
-    <t>CL21A476MQYNNNE</t>
-  </si>
-  <si>
-    <t>C0805</t>
-  </si>
-  <si>
-    <t>82.7mm</t>
-  </si>
-  <si>
-    <t>-88mm</t>
-  </si>
-  <si>
-    <t>83.73mm</t>
-  </si>
-  <si>
-    <t>47uF</t>
-  </si>
-  <si>
-    <t>C67</t>
-  </si>
-  <si>
-    <t>78mm</t>
-  </si>
-  <si>
-    <t>79.03mm</t>
-  </si>
-  <si>
-    <t>AUDIO1</t>
-  </si>
-  <si>
-    <t>PJ-3420-A-SMT</t>
-  </si>
-  <si>
-    <t>AUDIO-SMD_PJ-3420-A-SMT_C319102</t>
-  </si>
-  <si>
-    <t>82.2mm</t>
-  </si>
-  <si>
-    <t>-81.5mm</t>
-  </si>
-  <si>
-    <t>86.9mm</t>
-  </si>
-  <si>
-    <t>-78mm</t>
-  </si>
-  <si>
-    <t>J7</t>
-  </si>
-  <si>
-    <t>74.5mm</t>
-  </si>
-  <si>
-    <t>-87.31mm</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>HDR-M_2.54_1x2P</t>
-  </si>
-  <si>
-    <t>SMT wire pad (2)</t>
-  </si>
-  <si>
-    <t>21.87mm</t>
-  </si>
-  <si>
-    <t>-93.7mm</t>
-  </si>
-  <si>
-    <t>20.6mm</t>
-  </si>
-  <si>
-    <t>B-2100S02P-A110</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>RCKid2 Cartridge Connector Female</t>
-  </si>
-  <si>
-    <t>RCKid Cartridge Riser</t>
-  </si>
-  <si>
-    <t>79.25mm</t>
-  </si>
-  <si>
-    <t>-43mm</t>
-  </si>
-  <si>
-    <t>79.5mm</t>
-  </si>
-  <si>
-    <t>79mm</t>
-  </si>
-  <si>
-    <t>-17.6mm</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>ST7789V 2.8" IPS 320x240 37P 8080 8bit</t>
-  </si>
-  <si>
-    <t>ST7789V 2.8" IPS DISPLAY 320X240 37P</t>
-  </si>
-  <si>
-    <t>28.25mm</t>
-  </si>
-  <si>
-    <t>-25.1mm</t>
-  </si>
-  <si>
-    <t>-0.75mm</t>
-  </si>
-  <si>
-    <t>-49mm</t>
-  </si>
-  <si>
-    <t>-7.1mm</t>
-  </si>
-  <si>
-    <t>ST7789V 2.8&amp;quot; IPS 320x240 37P 8080 8bit</t>
-  </si>
-  <si>
-    <t>C137</t>
-  </si>
-  <si>
-    <t>22.3mm</t>
-  </si>
-  <si>
-    <t>0.7mm</t>
-  </si>
-  <si>
-    <t>21.27mm</t>
-  </si>
-  <si>
-    <t>C138</t>
-  </si>
-  <si>
-    <t>CL05A475MP5NRNC</t>
-  </si>
-  <si>
-    <t>34.7mm</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>R65</t>
-  </si>
-  <si>
-    <t>0805W8F100KT5E</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>30.9mm</t>
-  </si>
-  <si>
-    <t>31.9mm</t>
-  </si>
-  <si>
-    <t>1Ω</t>
-  </si>
-  <si>
-    <t>C136</t>
-  </si>
-  <si>
-    <t>26.7mm</t>
-  </si>
-  <si>
-    <t>27.73mm</t>
-  </si>
-  <si>
-    <t>TF1</t>
-  </si>
-  <si>
-    <t>DM3CS-SF</t>
-  </si>
-  <si>
-    <t>TF-SMD_DM3CS-SF</t>
-  </si>
-  <si>
-    <t>-83mm</t>
-  </si>
-  <si>
-    <t>31.875mm</t>
-  </si>
-  <si>
-    <t>-76.65mm</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>24.6mm</t>
-  </si>
-  <si>
-    <t>-71.4mm</t>
-  </si>
-  <si>
-    <t>23.771mm</t>
-  </si>
-  <si>
-    <t>-70.571mm</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>23.4mm</t>
-  </si>
-  <si>
-    <t>-72.6mm</t>
-  </si>
-  <si>
-    <t>22.571mm</t>
-  </si>
-  <si>
-    <t>-71.771mm</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>22.2mm</t>
-  </si>
-  <si>
-    <t>-73.8mm</t>
-  </si>
-  <si>
-    <t>21.371mm</t>
-  </si>
-  <si>
-    <t>-72.971mm</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>25.8mm</t>
-  </si>
-  <si>
-    <t>-70.2mm</t>
-  </si>
-  <si>
-    <t>24.971mm</t>
-  </si>
-  <si>
-    <t>-69.371mm</t>
-  </si>
-  <si>
-    <t>D9</t>
-  </si>
-  <si>
-    <t>52mm</t>
-  </si>
-  <si>
-    <t>-54.6mm</t>
-  </si>
-  <si>
-    <t>52.829mm</t>
-  </si>
-  <si>
-    <t>-53.771mm</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>66.9mm</t>
-  </si>
-  <si>
-    <t>-62.3mm</t>
-  </si>
-  <si>
-    <t>-61.127mm</t>
-  </si>
-  <si>
-    <t>D11</t>
-  </si>
-  <si>
-    <t>54.9mm</t>
-  </si>
-  <si>
-    <t>-82.5mm</t>
-  </si>
-  <si>
-    <t>53.727mm</t>
-  </si>
-  <si>
-    <t>D12</t>
-  </si>
-  <si>
-    <t>26mm</t>
-  </si>
-  <si>
-    <t>-78.673mm</t>
-  </si>
-  <si>
-    <t>D14</t>
-  </si>
-  <si>
-    <t>65.7mm</t>
-  </si>
-  <si>
-    <t>66.873mm</t>
-  </si>
-  <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>-72.5mm</t>
-  </si>
-  <si>
-    <t>R67</t>
-  </si>
-  <si>
-    <t>62.9mm</t>
-  </si>
-  <si>
-    <t>-81.3mm</t>
-  </si>
-  <si>
-    <t>62.467mm</t>
-  </si>
-  <si>
-    <t>R69</t>
-  </si>
-  <si>
-    <t>0402WGF2200TCE</t>
-  </si>
-  <si>
-    <t>14.6mm</t>
-  </si>
-  <si>
-    <t>220Ω</t>
-  </si>
-  <si>
-    <t>R70</t>
-  </si>
-  <si>
-    <t>13.3mm</t>
-  </si>
-  <si>
-    <t>R71</t>
-  </si>
-  <si>
-    <t>0603WAF1801T5E</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>-87.3mm</t>
-  </si>
-  <si>
-    <t>86.147mm</t>
-  </si>
-  <si>
-    <t>1.8kΩ</t>
-  </si>
-  <si>
-    <t>R72</t>
-  </si>
-  <si>
-    <t>-88.9mm</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>-85.5mm</t>
-  </si>
-  <si>
-    <t>25mm</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>51mm</t>
-  </si>
-  <si>
-    <t>R74</t>
-  </si>
-  <si>
-    <t>55.967mm</t>
-  </si>
-  <si>
-    <t>HOME</t>
-  </si>
-  <si>
-    <t>B3U-3000PM-B</t>
-  </si>
-  <si>
-    <t>KEY-SMD_B3U-3000PM-B</t>
-  </si>
-  <si>
-    <t>66.8mm</t>
-  </si>
-  <si>
-    <t>-44.5mm</t>
-  </si>
-  <si>
-    <t>-46.5mm</t>
-  </si>
-  <si>
-    <t>VOL_UP</t>
-  </si>
-  <si>
-    <t>-65mm</t>
-  </si>
-  <si>
-    <t>VOL_DOWN</t>
-  </si>
-  <si>
-    <t>-75mm</t>
-  </si>
-  <si>
-    <t>-77mm</t>
-  </si>
-  <si>
-    <t>SPKR</t>
-  </si>
-  <si>
-    <t>9.3mm</t>
-  </si>
-  <si>
-    <t>-92.87mm</t>
-  </si>
-  <si>
-    <t>-91.6mm</t>
-  </si>
-  <si>
-    <t>R48</t>
-  </si>
-  <si>
-    <t>58.2mm</t>
-  </si>
-  <si>
-    <t>-68.8mm</t>
-  </si>
-  <si>
-    <t>58.633mm</t>
-  </si>
-  <si>
-    <t>B+</t>
-  </si>
-  <si>
-    <t>HDR-M_2.54_1x1P</t>
-  </si>
-  <si>
-    <t>HDR-TH_1P-V-M_XKB_X4611WV-01I-C28D40</t>
-  </si>
-  <si>
-    <t>66.7mm</t>
-  </si>
-  <si>
-    <t>-82.1mm</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>-87.2mm</t>
-  </si>
-  <si>
-    <t>R76</t>
-  </si>
-  <si>
-    <t>39.1mm</t>
-  </si>
-  <si>
-    <t>-71.933mm</t>
-  </si>
-  <si>
-    <t>R77</t>
-  </si>
-  <si>
-    <t>35.8mm</t>
-  </si>
-  <si>
-    <t>-67.467mm</t>
-  </si>
-  <si>
-    <t>R78</t>
-  </si>
-  <si>
-    <t>36.9mm</t>
-  </si>
-  <si>
-    <t>-71.067mm</t>
-  </si>
-  <si>
-    <t>R79</t>
-  </si>
-  <si>
-    <t>38mm</t>
-  </si>
-  <si>
-    <t>R80</t>
-  </si>
-  <si>
-    <t>40.2mm</t>
-  </si>
-  <si>
-    <t>U31</t>
-  </si>
-  <si>
-    <t>ATTINY3217-MFR</t>
-  </si>
-  <si>
-    <t>WQFN-24_L4.0-W4.0-P0.50-TL-EP2.6</t>
-  </si>
-  <si>
-    <t>48.6mm</t>
-  </si>
-  <si>
-    <t>-58.6mm</t>
-  </si>
-  <si>
-    <t>47.35mm</t>
-  </si>
-  <si>
-    <t>-60.625mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>INA219AIDCNR</t>
-  </si>
-  <si>
-    <t>SOT-23-8_L3.0-W1.7-P0.65-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>55.4mm</t>
-  </si>
-  <si>
-    <t>56.626mm</t>
-  </si>
-  <si>
-    <t>-88.675mm</t>
-  </si>
-  <si>
-    <t>R81</t>
-  </si>
-  <si>
-    <t>RTT05R010FTP</t>
-  </si>
-  <si>
-    <t>58.6mm</t>
-  </si>
-  <si>
-    <t>-88.7mm</t>
-  </si>
-  <si>
-    <t>10mΩ</t>
-  </si>
-  <si>
-    <t>D16</t>
-  </si>
-  <si>
-    <t>BAT60JFILM</t>
-  </si>
-  <si>
-    <t>60.6mm</t>
-  </si>
-  <si>
-    <t>-88.873mm</t>
-  </si>
-  <si>
-    <t>U32</t>
-  </si>
-  <si>
-    <t>MCP73832T-2ACI/OT</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>63.1mm</t>
-  </si>
-  <si>
-    <t>-83.8mm</t>
-  </si>
-  <si>
-    <t>64.4mm</t>
-  </si>
-  <si>
-    <t>-84.75mm</t>
-  </si>
-  <si>
-    <t>C142</t>
-  </si>
-  <si>
-    <t>56.1mm</t>
-  </si>
-  <si>
-    <t>56.645mm</t>
-  </si>
-  <si>
-    <t>R83</t>
-  </si>
-  <si>
-    <t>46.4mm</t>
-  </si>
-  <si>
-    <t>-55mm</t>
-  </si>
-  <si>
-    <t>46.833mm</t>
-  </si>
-  <si>
-    <t>R84</t>
-  </si>
-  <si>
-    <t>WR04W5R11FTL</t>
-  </si>
-  <si>
-    <t>7.6mm</t>
-  </si>
-  <si>
-    <t>-56.2mm</t>
-  </si>
-  <si>
-    <t>7.906mm</t>
-  </si>
-  <si>
-    <t>-55.894mm</t>
-  </si>
-  <si>
-    <t>5.11Ω</t>
-  </si>
-  <si>
-    <t>R86</t>
-  </si>
-  <si>
-    <t>57.3mm</t>
-  </si>
-  <si>
-    <t>56.867mm</t>
-  </si>
-  <si>
-    <t>U33</t>
-  </si>
-  <si>
-    <t>SN74LVC1T45DBVR</t>
-  </si>
-  <si>
-    <t>-71.9mm</t>
-  </si>
-  <si>
-    <t>62.75mm</t>
-  </si>
-  <si>
-    <t>-72.85mm</t>
-  </si>
-  <si>
-    <t>C143</t>
-  </si>
-  <si>
-    <t>20mm</t>
-  </si>
-  <si>
-    <t>-80.2mm</t>
-  </si>
-  <si>
-    <t>-80.745mm</t>
-  </si>
-  <si>
-    <t>C144</t>
-  </si>
-  <si>
-    <t>-92.6mm</t>
-  </si>
-  <si>
-    <t>48.545mm</t>
-  </si>
-  <si>
-    <t>U34</t>
-  </si>
-  <si>
-    <t>TPS63001DRCR</t>
-  </si>
-  <si>
-    <t>VSON-10_L3.0-W3.0-P0.50-TL-EP_TPS62410DRCR</t>
-  </si>
-  <si>
-    <t>59.25mm</t>
-  </si>
-  <si>
-    <t>-76.54mm</t>
-  </si>
-  <si>
-    <t>58.25mm</t>
-  </si>
-  <si>
-    <t>-78.04mm</t>
-  </si>
-  <si>
-    <t>L13</t>
-  </si>
-  <si>
-    <t>NR3015T1R0N</t>
-  </si>
-  <si>
-    <t>IND-SMD_L3.0-W3.0_NR3010</t>
-  </si>
-  <si>
-    <t>59.3mm</t>
-  </si>
-  <si>
-    <t>-80.7mm</t>
-  </si>
-  <si>
-    <t>60.35mm</t>
-  </si>
-  <si>
-    <t>1uH</t>
-  </si>
-  <si>
-    <t>C145</t>
-  </si>
-  <si>
-    <t>CL10A106KP8NNNC</t>
-  </si>
-  <si>
-    <t>63.8mm</t>
-  </si>
-  <si>
-    <t>-77.4mm</t>
-  </si>
-  <si>
-    <t>-76.7mm</t>
-  </si>
-  <si>
-    <t>C146</t>
-  </si>
-  <si>
-    <t>51.3mm</t>
-  </si>
-  <si>
-    <t>C147</t>
-  </si>
-  <si>
-    <t>54.7mm</t>
-  </si>
-  <si>
-    <t>C148</t>
-  </si>
-  <si>
-    <t>53mm</t>
-  </si>
-  <si>
-    <t>C149</t>
-  </si>
-  <si>
-    <t>49.6mm</t>
-  </si>
-  <si>
-    <t>C150</t>
-  </si>
-  <si>
-    <t>55mm</t>
-  </si>
-  <si>
-    <t>55.7mm</t>
-  </si>
-  <si>
-    <t>C151</t>
-  </si>
-  <si>
-    <t>8.8mm</t>
-  </si>
-  <si>
-    <t>-78.8mm</t>
-  </si>
-  <si>
-    <t>-78.1mm</t>
-  </si>
-  <si>
-    <t>C152</t>
-  </si>
-  <si>
-    <t>10.6mm</t>
-  </si>
-  <si>
-    <t>LED7</t>
-  </si>
-  <si>
-    <t>XL-1615RGBC-WS2812B</t>
-  </si>
-  <si>
-    <t>LED-SMD_4P-L1.6-W1.5_XL-1615RGBC-WS2812B</t>
-  </si>
-  <si>
-    <t>53.7mm</t>
-  </si>
-  <si>
-    <t>54.15mm</t>
-  </si>
-  <si>
-    <t>-69.25mm</t>
-  </si>
-  <si>
-    <t>LED8</t>
-  </si>
-  <si>
-    <t>59.75mm</t>
-  </si>
-  <si>
-    <t>-54.05mm</t>
-  </si>
-  <si>
-    <t>LED9</t>
-  </si>
-  <si>
-    <t>52.25mm</t>
-  </si>
-  <si>
-    <t>2.35mm</t>
-  </si>
-  <si>
-    <t>LED10</t>
-  </si>
-  <si>
-    <t>15.25mm</t>
-  </si>
-  <si>
-    <t>-64.95mm</t>
-  </si>
-  <si>
-    <t>LED11</t>
-  </si>
-  <si>
-    <t>21.55mm</t>
-  </si>
-  <si>
-    <t>-80.95mm</t>
-  </si>
-  <si>
-    <t>LED12</t>
-  </si>
-  <si>
-    <t>-90.7mm</t>
-  </si>
-  <si>
-    <t>48.75mm</t>
-  </si>
-  <si>
-    <t>-91.15mm</t>
-  </si>
-  <si>
-    <t>R87</t>
-  </si>
-  <si>
-    <t>0402WGF4700TCE</t>
-  </si>
-  <si>
-    <t>56.833mm</t>
-  </si>
-  <si>
-    <t>470Ω</t>
-  </si>
-  <si>
-    <t>R88</t>
-  </si>
-  <si>
-    <t>50.1mm</t>
-  </si>
-  <si>
-    <t>-91.133mm</t>
+    <t>-77.965mm</t>
+  </si>
+  <si>
+    <t>R92</t>
+  </si>
+  <si>
+    <t>8.7mm</t>
+  </si>
+  <si>
+    <t>-74.6mm</t>
+  </si>
+  <si>
+    <t>8.394mm</t>
+  </si>
+  <si>
+    <t>-74.906mm</t>
+  </si>
+  <si>
+    <t>U35</t>
+  </si>
+  <si>
+    <t>86.15mm</t>
+  </si>
+  <si>
+    <t>86.4mm</t>
+  </si>
+  <si>
+    <t>85.9mm</t>
   </si>
 </sst>
 </file>
@@ -2457,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N157"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -5038,10 +5092,10 @@
         <v>282</v>
       </c>
       <c r="H59" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -5050,7 +5104,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
         <v>22</v>
@@ -5070,22 +5124,22 @@
         <v>91</v>
       </c>
       <c r="D60" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E60" t="s">
+        <v>286</v>
+      </c>
+      <c r="F60" t="s">
         <v>285</v>
       </c>
-      <c r="F60" t="s">
-        <v>281</v>
-      </c>
       <c r="G60" t="s">
+        <v>286</v>
+      </c>
+      <c r="H60" t="s">
         <v>285</v>
       </c>
-      <c r="H60" t="s">
-        <v>281</v>
-      </c>
       <c r="I60" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -5105,31 +5159,31 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B61" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C61" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E61" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G61" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="H61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -5149,31 +5203,31 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B62" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C62" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D62" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E62" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F62" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G62" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H62" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I62" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J62">
         <v>8</v>
@@ -5188,36 +5242,36 @@
         <v>22</v>
       </c>
       <c r="N62" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B63" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E63" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F63" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G63" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H63" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I63" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J63">
         <v>2</v>
@@ -5237,7 +5291,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s">
         <v>24</v>
@@ -5246,22 +5300,22 @@
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E64" t="s">
         <v>93</v>
       </c>
       <c r="F64" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G64" t="s">
         <v>93</v>
       </c>
       <c r="H64" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I64" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -5281,7 +5335,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B65" t="s">
         <v>24</v>
@@ -5290,22 +5344,22 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E65" t="s">
         <v>93</v>
       </c>
       <c r="F65" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G65" t="s">
         <v>93</v>
       </c>
       <c r="H65" t="s">
+        <v>308</v>
+      </c>
+      <c r="I65" t="s">
         <v>306</v>
-      </c>
-      <c r="I65" t="s">
-        <v>304</v>
       </c>
       <c r="J65">
         <v>2</v>
@@ -5325,7 +5379,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B66" t="s">
         <v>24</v>
@@ -5334,22 +5388,22 @@
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E66" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F66" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G66" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="H66" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J66">
         <v>2</v>
@@ -5369,75 +5423,75 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="s">
+        <v>312</v>
+      </c>
+      <c r="E67" t="s">
+        <v>313</v>
+      </c>
+      <c r="F67" t="s">
+        <v>312</v>
+      </c>
+      <c r="G67" t="s">
+        <v>313</v>
+      </c>
+      <c r="H67" t="s">
+        <v>312</v>
+      </c>
+      <c r="I67" t="s">
+        <v>314</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67">
         <v>90</v>
       </c>
-      <c r="C67" t="s">
-        <v>91</v>
-      </c>
-      <c r="D67" t="s">
-        <v>310</v>
-      </c>
-      <c r="E67" t="s">
-        <v>285</v>
-      </c>
-      <c r="F67" t="s">
-        <v>310</v>
-      </c>
-      <c r="G67" t="s">
-        <v>285</v>
-      </c>
-      <c r="H67" t="s">
-        <v>310</v>
-      </c>
-      <c r="I67" t="s">
-        <v>311</v>
-      </c>
-      <c r="J67">
-        <v>2</v>
-      </c>
-      <c r="K67" t="s">
-        <v>21</v>
-      </c>
-      <c r="L67">
-        <v>270</v>
-      </c>
       <c r="M67" t="s">
         <v>22</v>
       </c>
       <c r="N67" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="C68" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="E68" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F68" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="G68" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H68" t="s">
-        <v>313</v>
+        <v>275</v>
       </c>
       <c r="I68" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J68">
         <v>2</v>
@@ -5446,18 +5500,18 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M68" t="s">
         <v>22</v>
       </c>
       <c r="N68" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B69" t="s">
         <v>171</v>
@@ -5466,22 +5520,22 @@
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="E69" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="F69" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="G69" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="H69" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="I69" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J69">
         <v>2</v>
@@ -5501,119 +5555,119 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>321</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>322</v>
       </c>
       <c r="D70" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="E70" t="s">
-        <v>319</v>
+        <v>68</v>
       </c>
       <c r="F70" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="G70" t="s">
-        <v>319</v>
+        <v>68</v>
       </c>
       <c r="H70" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="I70" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K70" t="s">
         <v>21</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M70" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="N70" t="s">
-        <v>175</v>
+        <v>325</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B71" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C71" t="s">
-        <v>322</v>
+        <v>91</v>
       </c>
       <c r="D71" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="E71" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="G71" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="H71" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="I71" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K71" t="s">
         <v>21</v>
       </c>
       <c r="L71">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M71" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="N71" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C72" t="s">
         <v>91</v>
       </c>
       <c r="D72" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E72" t="s">
         <v>151</v>
       </c>
       <c r="F72" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G72" t="s">
         <v>151</v>
       </c>
       <c r="H72" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J72">
         <v>2</v>
@@ -5628,36 +5682,36 @@
         <v>22</v>
       </c>
       <c r="N72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B73" t="s">
-        <v>326</v>
+        <v>90</v>
       </c>
       <c r="C73" t="s">
         <v>91</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
       <c r="F73" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G73" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
       <c r="H73" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I73" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="J73">
         <v>2</v>
@@ -5666,42 +5720,42 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M73" t="s">
         <v>22</v>
       </c>
       <c r="N73" t="s">
-        <v>329</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B74" t="s">
-        <v>90</v>
+        <v>338</v>
       </c>
       <c r="C74" t="s">
-        <v>91</v>
+        <v>339</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E74" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F74" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="G74" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="H74" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="I74" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="J74">
         <v>2</v>
@@ -5710,106 +5764,106 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M74" t="s">
         <v>22</v>
       </c>
       <c r="N74" t="s">
-        <v>95</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B75" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C75" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E75" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F75" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="G75" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="H75" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="I75" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" t="s">
         <v>21</v>
       </c>
       <c r="L75">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="M75" t="s">
         <v>22</v>
       </c>
       <c r="N75" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B76" t="s">
-        <v>344</v>
+        <v>90</v>
       </c>
       <c r="C76" t="s">
-        <v>345</v>
+        <v>91</v>
       </c>
       <c r="D76" t="s">
-        <v>346</v>
+        <v>61</v>
       </c>
       <c r="E76" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="F76" t="s">
-        <v>348</v>
+        <v>61</v>
       </c>
       <c r="G76" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="H76" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I76" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76" t="s">
         <v>21</v>
       </c>
       <c r="L76">
-        <v>315</v>
+        <v>225</v>
       </c>
       <c r="M76" t="s">
         <v>22</v>
       </c>
       <c r="N76" t="s">
-        <v>352</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B77" t="s">
         <v>90</v>
@@ -5818,22 +5872,22 @@
         <v>91</v>
       </c>
       <c r="D77" t="s">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="E77" t="s">
-        <v>354</v>
+        <v>151</v>
       </c>
       <c r="F77" t="s">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="G77" t="s">
-        <v>354</v>
+        <v>151</v>
       </c>
       <c r="H77" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I77" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="J77">
         <v>2</v>
@@ -5842,7 +5896,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="M77" t="s">
         <v>22</v>
@@ -5853,295 +5907,295 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="C78" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D78" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E78" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F78" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G78" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H78" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I78" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" t="s">
         <v>21</v>
       </c>
       <c r="L78">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M78" t="s">
         <v>22</v>
       </c>
       <c r="N78" t="s">
-        <v>193</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E79" t="s">
-        <v>151</v>
+        <v>368</v>
       </c>
       <c r="F79" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="G79" t="s">
-        <v>151</v>
+        <v>368</v>
       </c>
       <c r="H79" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I79" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K79" t="s">
         <v>21</v>
       </c>
       <c r="L79">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M79" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="N79" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B80" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D80" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E80" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F80" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G80" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="H80" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="I80" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="J80">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K80" t="s">
         <v>21</v>
       </c>
       <c r="L80">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M80" t="s">
         <v>22</v>
       </c>
       <c r="N80" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="D81" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E81" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="F81" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G81" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="H81" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="I81" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K81" t="s">
         <v>21</v>
       </c>
       <c r="L81">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M81" t="s">
         <v>88</v>
       </c>
       <c r="N81" t="s">
-        <v>83</v>
+        <v>378</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B82" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
+        <v>91</v>
       </c>
       <c r="D82" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="E82" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="F82" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="G82" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="H82" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="I82" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="J82">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K82" t="s">
         <v>21</v>
       </c>
       <c r="L82">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M82" t="s">
         <v>22</v>
       </c>
       <c r="N82" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B83" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C83" t="s">
-        <v>382</v>
+        <v>91</v>
       </c>
       <c r="D83" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E83" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F83" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G83" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="H83" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I83" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J83">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K83" t="s">
         <v>21</v>
       </c>
       <c r="L83">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="N83" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B84" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>394</v>
       </c>
       <c r="D84" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E84" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F84" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G84" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H84" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I84" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="J84">
         <v>2</v>
@@ -6150,42 +6204,42 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M84" t="s">
         <v>22</v>
       </c>
       <c r="N84" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>399</v>
+      </c>
+      <c r="B85" t="s">
         <v>393</v>
       </c>
-      <c r="B85" t="s">
-        <v>388</v>
-      </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>394</v>
       </c>
       <c r="D85" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E85" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F85" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="G85" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H85" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="I85" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J85">
         <v>2</v>
@@ -6194,45 +6248,45 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M85" t="s">
         <v>22</v>
       </c>
       <c r="N85" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B86" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C86" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D86" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E86" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F86" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="G86" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="H86" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="I86" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="J86">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K86" t="s">
         <v>21</v>
@@ -6244,215 +6298,215 @@
         <v>22</v>
       </c>
       <c r="N86" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B87" t="s">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="C87" t="s">
-        <v>397</v>
+        <v>84</v>
       </c>
       <c r="D87" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E87" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F87" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="G87" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="H87" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I87" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="J87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K87" t="s">
         <v>21</v>
       </c>
       <c r="L87">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M87" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="N87" t="s">
-        <v>401</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B88" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C88" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D88" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="E88" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F88" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="G88" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="H88" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="I88" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="J88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K88" t="s">
         <v>21</v>
       </c>
       <c r="L88">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M88" t="s">
         <v>22</v>
       </c>
       <c r="N88" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="D89" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="E89" t="s">
-        <v>285</v>
+        <v>424</v>
       </c>
       <c r="F89" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="G89" t="s">
-        <v>285</v>
+        <v>424</v>
       </c>
       <c r="H89" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="I89" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="J89">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K89" t="s">
         <v>21</v>
       </c>
       <c r="L89">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M89" t="s">
         <v>88</v>
       </c>
       <c r="N89" t="s">
-        <v>83</v>
+        <v>421</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B90" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="C90" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="D90" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="E90" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="F90" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="G90" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="H90" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="I90" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="J90">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="K90" t="s">
         <v>21</v>
       </c>
       <c r="L90">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M90" t="s">
         <v>22</v>
       </c>
       <c r="N90" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="C91" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="D91" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="E91" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F91" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="G91" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="H91" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="I91" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="J91">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K91" t="s">
         <v>21</v>
@@ -6461,83 +6515,83 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="N91" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B92" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C92" t="s">
-        <v>432</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="E92" t="s">
-        <v>434</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="G92" t="s">
-        <v>436</v>
+        <v>36</v>
       </c>
       <c r="H92" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="I92" t="s">
-        <v>437</v>
+        <v>37</v>
       </c>
       <c r="J92">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="K92" t="s">
         <v>21</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M92" t="s">
         <v>22</v>
       </c>
       <c r="N92" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>445</v>
+      </c>
+      <c r="B93" t="s">
+        <v>446</v>
+      </c>
+      <c r="C93" t="s">
+        <v>447</v>
+      </c>
+      <c r="D93" t="s">
+        <v>448</v>
+      </c>
+      <c r="E93" t="s">
         <v>439</v>
       </c>
-      <c r="B93" t="s">
-        <v>396</v>
-      </c>
-      <c r="C93" t="s">
-        <v>397</v>
-      </c>
-      <c r="D93" t="s">
-        <v>440</v>
-      </c>
-      <c r="E93" t="s">
-        <v>441</v>
-      </c>
       <c r="F93" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="G93" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H93" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="I93" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J93">
         <v>2</v>
@@ -6546,42 +6600,42 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M93" t="s">
         <v>22</v>
       </c>
       <c r="N93" t="s">
-        <v>401</v>
+        <v>450</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B94" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>394</v>
       </c>
       <c r="D94" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E94" t="s">
-        <v>36</v>
+        <v>439</v>
       </c>
       <c r="F94" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G94" t="s">
-        <v>36</v>
+        <v>439</v>
       </c>
       <c r="H94" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="I94" t="s">
-        <v>37</v>
+        <v>439</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -6590,45 +6644,45 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M94" t="s">
         <v>22</v>
       </c>
       <c r="N94" t="s">
-        <v>446</v>
+        <v>398</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B95" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C95" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D95" t="s">
-        <v>450</v>
+        <v>48</v>
       </c>
       <c r="E95" t="s">
-        <v>441</v>
+        <v>291</v>
       </c>
       <c r="F95" t="s">
-        <v>450</v>
+        <v>48</v>
       </c>
       <c r="G95" t="s">
-        <v>441</v>
+        <v>291</v>
       </c>
       <c r="H95" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="I95" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K95" t="s">
         <v>21</v>
@@ -6640,36 +6694,36 @@
         <v>22</v>
       </c>
       <c r="N95" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B96" t="s">
-        <v>396</v>
+        <v>338</v>
       </c>
       <c r="C96" t="s">
-        <v>397</v>
+        <v>339</v>
       </c>
       <c r="D96" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E96" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="F96" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="G96" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="H96" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="I96" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="J96">
         <v>2</v>
@@ -6678,86 +6732,86 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="M96" t="s">
         <v>22</v>
       </c>
       <c r="N96" t="s">
-        <v>401</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B97" t="s">
-        <v>457</v>
+        <v>338</v>
       </c>
       <c r="C97" t="s">
-        <v>458</v>
+        <v>339</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>465</v>
       </c>
       <c r="E97" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="F97" t="s">
-        <v>48</v>
+        <v>465</v>
       </c>
       <c r="G97" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="H97" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="I97" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="J97">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K97" t="s">
         <v>21</v>
       </c>
       <c r="L97">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="M97" t="s">
         <v>22</v>
       </c>
       <c r="N97" t="s">
-        <v>457</v>
+        <v>343</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B98" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C98" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D98" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E98" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F98" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="G98" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="H98" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="I98" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="J98">
         <v>2</v>
@@ -6772,36 +6826,36 @@
         <v>22</v>
       </c>
       <c r="N98" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B99" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C99" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D99" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E99" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F99" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="G99" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="H99" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="I99" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="J99">
         <v>2</v>
@@ -6816,36 +6870,36 @@
         <v>22</v>
       </c>
       <c r="N99" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B100" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C100" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D100" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E100" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F100" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="G100" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="H100" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="I100" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="J100">
         <v>2</v>
@@ -6854,42 +6908,42 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>315</v>
+        <v>225</v>
       </c>
       <c r="M100" t="s">
         <v>22</v>
       </c>
       <c r="N100" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B101" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C101" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D101" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E101" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F101" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="G101" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="H101" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I101" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="J101">
         <v>2</v>
@@ -6898,42 +6952,42 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>315</v>
+        <v>270</v>
       </c>
       <c r="M101" t="s">
         <v>22</v>
       </c>
       <c r="N101" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C102" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D102" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E102" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F102" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="G102" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="H102" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="I102" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J102">
         <v>2</v>
@@ -6942,42 +6996,42 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M102" t="s">
         <v>22</v>
       </c>
       <c r="N102" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D103" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E103" t="s">
-        <v>489</v>
+        <v>239</v>
       </c>
       <c r="F103" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="G103" t="s">
-        <v>489</v>
+        <v>239</v>
       </c>
       <c r="H103" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="I103" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -6986,42 +7040,42 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M103" t="s">
         <v>22</v>
       </c>
       <c r="N103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B104" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C104" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D104" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E104" t="s">
-        <v>493</v>
+        <v>98</v>
       </c>
       <c r="F104" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G104" t="s">
-        <v>493</v>
+        <v>98</v>
       </c>
       <c r="H104" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="I104" t="s">
-        <v>493</v>
+        <v>98</v>
       </c>
       <c r="J104">
         <v>2</v>
@@ -7030,42 +7084,42 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M104" t="s">
         <v>22</v>
       </c>
       <c r="N104" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B105" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C105" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
         <v>496</v>
       </c>
       <c r="E105" t="s">
-        <v>239</v>
+        <v>499</v>
       </c>
       <c r="F105" t="s">
         <v>496</v>
       </c>
       <c r="G105" t="s">
-        <v>239</v>
+        <v>499</v>
       </c>
       <c r="H105" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I105" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J105">
         <v>2</v>
@@ -7074,42 +7128,42 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M105" t="s">
         <v>22</v>
       </c>
       <c r="N105" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B106" t="s">
-        <v>337</v>
+        <v>90</v>
       </c>
       <c r="C106" t="s">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="D106" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E106" t="s">
-        <v>98</v>
+        <v>502</v>
       </c>
       <c r="F106" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G106" t="s">
-        <v>98</v>
+        <v>502</v>
       </c>
       <c r="H106" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I106" t="s">
-        <v>98</v>
+        <v>502</v>
       </c>
       <c r="J106">
         <v>2</v>
@@ -7118,42 +7172,42 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M106" t="s">
         <v>22</v>
       </c>
       <c r="N106" t="s">
-        <v>342</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B107" t="s">
-        <v>337</v>
+        <v>505</v>
       </c>
       <c r="C107" t="s">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="D107" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E107" t="s">
-        <v>502</v>
+        <v>93</v>
       </c>
       <c r="F107" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="G107" t="s">
-        <v>502</v>
+        <v>93</v>
       </c>
       <c r="H107" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="I107" t="s">
-        <v>502</v>
+        <v>94</v>
       </c>
       <c r="J107">
         <v>2</v>
@@ -7162,42 +7216,42 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M107" t="s">
         <v>22</v>
       </c>
       <c r="N107" t="s">
-        <v>342</v>
+        <v>507</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B108" t="s">
-        <v>90</v>
+        <v>505</v>
       </c>
       <c r="C108" t="s">
         <v>91</v>
       </c>
       <c r="D108" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E108" t="s">
-        <v>505</v>
+        <v>93</v>
       </c>
       <c r="F108" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="G108" t="s">
-        <v>505</v>
+        <v>93</v>
       </c>
       <c r="H108" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="I108" t="s">
-        <v>505</v>
+        <v>94</v>
       </c>
       <c r="J108">
         <v>2</v>
@@ -7206,42 +7260,42 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M108" t="s">
         <v>22</v>
       </c>
       <c r="N108" t="s">
-        <v>95</v>
+        <v>507</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B109" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C109" t="s">
-        <v>91</v>
+        <v>512</v>
       </c>
       <c r="D109" t="s">
-        <v>509</v>
+        <v>407</v>
       </c>
       <c r="E109" t="s">
-        <v>93</v>
+        <v>513</v>
       </c>
       <c r="F109" t="s">
-        <v>509</v>
+        <v>407</v>
       </c>
       <c r="G109" t="s">
-        <v>93</v>
+        <v>513</v>
       </c>
       <c r="H109" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="I109" t="s">
-        <v>94</v>
+        <v>513</v>
       </c>
       <c r="J109">
         <v>2</v>
@@ -7250,42 +7304,42 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M109" t="s">
         <v>22</v>
       </c>
       <c r="N109" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>516</v>
+      </c>
+      <c r="B110" t="s">
         <v>511</v>
       </c>
-      <c r="B110" t="s">
-        <v>508</v>
-      </c>
       <c r="C110" t="s">
-        <v>91</v>
+        <v>512</v>
       </c>
       <c r="D110" t="s">
-        <v>512</v>
+        <v>407</v>
       </c>
       <c r="E110" t="s">
-        <v>93</v>
+        <v>517</v>
       </c>
       <c r="F110" t="s">
-        <v>512</v>
+        <v>407</v>
       </c>
       <c r="G110" t="s">
-        <v>93</v>
+        <v>517</v>
       </c>
       <c r="H110" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I110" t="s">
-        <v>94</v>
+        <v>517</v>
       </c>
       <c r="J110">
         <v>2</v>
@@ -7294,262 +7348,262 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M110" t="s">
         <v>22</v>
       </c>
       <c r="N110" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B111" t="s">
-        <v>514</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>515</v>
+        <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>410</v>
+        <v>70</v>
       </c>
       <c r="E111" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F111" t="s">
-        <v>410</v>
+        <v>70</v>
       </c>
       <c r="G111" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H111" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="I111" t="s">
-        <v>516</v>
+        <v>396</v>
       </c>
       <c r="J111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K111" t="s">
         <v>21</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M111" t="s">
         <v>22</v>
       </c>
       <c r="N111" t="s">
-        <v>518</v>
+        <v>54</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>521</v>
+      </c>
+      <c r="B112" t="s">
+        <v>54</v>
+      </c>
+      <c r="C112" t="s">
+        <v>55</v>
+      </c>
+      <c r="D112" t="s">
+        <v>74</v>
+      </c>
+      <c r="E112" t="s">
         <v>519</v>
       </c>
-      <c r="B112" t="s">
-        <v>514</v>
-      </c>
-      <c r="C112" t="s">
-        <v>515</v>
-      </c>
-      <c r="D112" t="s">
-        <v>410</v>
-      </c>
-      <c r="E112" t="s">
-        <v>520</v>
-      </c>
       <c r="F112" t="s">
-        <v>410</v>
+        <v>74</v>
       </c>
       <c r="G112" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H112" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="I112" t="s">
-        <v>520</v>
+        <v>396</v>
       </c>
       <c r="J112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K112" t="s">
         <v>21</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M112" t="s">
         <v>22</v>
       </c>
       <c r="N112" t="s">
-        <v>518</v>
+        <v>54</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B113" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="C113" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="D113" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E113" t="s">
-        <v>522</v>
+        <v>350</v>
       </c>
       <c r="F113" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="G113" t="s">
-        <v>522</v>
+        <v>350</v>
       </c>
       <c r="H113" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I113" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="J113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K113" t="s">
         <v>21</v>
       </c>
       <c r="L113">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M113" t="s">
         <v>22</v>
       </c>
       <c r="N113" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>526</v>
       </c>
       <c r="C114" t="s">
-        <v>55</v>
+        <v>527</v>
       </c>
       <c r="D114" t="s">
-        <v>74</v>
+        <v>528</v>
       </c>
       <c r="E114" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="F114" t="s">
-        <v>74</v>
+        <v>528</v>
       </c>
       <c r="G114" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="H114" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="I114" t="s">
-        <v>399</v>
+        <v>530</v>
       </c>
       <c r="J114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="L114">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M114" t="s">
         <v>22</v>
       </c>
       <c r="N114" t="s">
-        <v>54</v>
+        <v>526</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>531</v>
+      </c>
+      <c r="B115" t="s">
         <v>526</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
+        <v>527</v>
+      </c>
+      <c r="D115" t="s">
+        <v>528</v>
+      </c>
+      <c r="E115" t="s">
+        <v>532</v>
+      </c>
+      <c r="F115" t="s">
+        <v>528</v>
+      </c>
+      <c r="G115" t="s">
+        <v>532</v>
+      </c>
+      <c r="H115" t="s">
+        <v>528</v>
+      </c>
+      <c r="I115" t="s">
+        <v>209</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115" t="s">
+        <v>122</v>
+      </c>
+      <c r="L115">
         <v>90</v>
       </c>
-      <c r="C115" t="s">
-        <v>91</v>
-      </c>
-      <c r="D115" t="s">
-        <v>97</v>
-      </c>
-      <c r="E115" t="s">
-        <v>349</v>
-      </c>
-      <c r="F115" t="s">
-        <v>97</v>
-      </c>
-      <c r="G115" t="s">
-        <v>349</v>
-      </c>
-      <c r="H115" t="s">
-        <v>527</v>
-      </c>
-      <c r="I115" t="s">
-        <v>349</v>
-      </c>
-      <c r="J115">
-        <v>2</v>
-      </c>
-      <c r="K115" t="s">
-        <v>21</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
       <c r="M115" t="s">
         <v>22</v>
       </c>
       <c r="N115" t="s">
-        <v>95</v>
+        <v>526</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>533</v>
+      </c>
+      <c r="B116" t="s">
+        <v>526</v>
+      </c>
+      <c r="C116" t="s">
+        <v>527</v>
+      </c>
+      <c r="D116" t="s">
         <v>528</v>
       </c>
-      <c r="B116" t="s">
-        <v>529</v>
-      </c>
-      <c r="C116" t="s">
-        <v>530</v>
-      </c>
-      <c r="D116" t="s">
-        <v>531</v>
-      </c>
       <c r="E116" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F116" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="G116" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H116" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I116" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J116">
         <v>2</v>
@@ -7564,215 +7618,215 @@
         <v>22</v>
       </c>
       <c r="N116" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B117" t="s">
-        <v>529</v>
+        <v>414</v>
       </c>
       <c r="C117" t="s">
-        <v>530</v>
+        <v>415</v>
       </c>
       <c r="D117" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E117" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F117" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="G117" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="H117" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="I117" t="s">
-        <v>209</v>
+        <v>539</v>
       </c>
       <c r="J117">
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="L117">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M117" t="s">
         <v>22</v>
       </c>
       <c r="N117" t="s">
-        <v>529</v>
+        <v>419</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B118" t="s">
-        <v>529</v>
+        <v>90</v>
       </c>
       <c r="C118" t="s">
-        <v>530</v>
+        <v>91</v>
       </c>
       <c r="D118" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="E118" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F118" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="G118" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="H118" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="I118" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="J118">
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="L118">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M118" t="s">
         <v>22</v>
       </c>
       <c r="N118" t="s">
-        <v>529</v>
+        <v>95</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B119" t="s">
-        <v>416</v>
+        <v>545</v>
       </c>
       <c r="C119" t="s">
-        <v>417</v>
+        <v>546</v>
       </c>
       <c r="D119" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E119" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F119" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="G119" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="H119" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="I119" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K119" t="s">
         <v>21</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M119" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="N119" t="s">
-        <v>421</v>
+        <v>545</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B120" t="s">
-        <v>90</v>
+        <v>545</v>
       </c>
       <c r="C120" t="s">
-        <v>91</v>
+        <v>546</v>
       </c>
       <c r="D120" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E120" t="s">
+        <v>550</v>
+      </c>
+      <c r="F120" t="s">
+        <v>547</v>
+      </c>
+      <c r="G120" t="s">
+        <v>550</v>
+      </c>
+      <c r="H120" t="s">
+        <v>547</v>
+      </c>
+      <c r="I120" t="s">
+        <v>550</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120" t="s">
+        <v>21</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" t="s">
+        <v>88</v>
+      </c>
+      <c r="N120" t="s">
         <v>545</v>
-      </c>
-      <c r="F120" t="s">
-        <v>544</v>
-      </c>
-      <c r="G120" t="s">
-        <v>545</v>
-      </c>
-      <c r="H120" t="s">
-        <v>546</v>
-      </c>
-      <c r="I120" t="s">
-        <v>545</v>
-      </c>
-      <c r="J120">
-        <v>2</v>
-      </c>
-      <c r="K120" t="s">
-        <v>21</v>
-      </c>
-      <c r="L120">
-        <v>180</v>
-      </c>
-      <c r="M120" t="s">
-        <v>22</v>
-      </c>
-      <c r="N120" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B121" t="s">
-        <v>548</v>
+        <v>90</v>
       </c>
       <c r="C121" t="s">
-        <v>549</v>
+        <v>91</v>
       </c>
       <c r="D121" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E121" t="s">
-        <v>551</v>
+        <v>363</v>
       </c>
       <c r="F121" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G121" t="s">
-        <v>551</v>
+        <v>363</v>
       </c>
       <c r="H121" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I121" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" t="s">
         <v>21</v>
@@ -7781,83 +7835,83 @@
         <v>90</v>
       </c>
       <c r="M121" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="N121" t="s">
-        <v>548</v>
+        <v>95</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B122" t="s">
-        <v>548</v>
+        <v>181</v>
       </c>
       <c r="C122" t="s">
-        <v>549</v>
+        <v>91</v>
       </c>
       <c r="D122" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E122" t="s">
-        <v>553</v>
+        <v>198</v>
       </c>
       <c r="F122" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="G122" t="s">
-        <v>553</v>
+        <v>198</v>
       </c>
       <c r="H122" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="I122" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K122" t="s">
         <v>21</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M122" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="N122" t="s">
-        <v>548</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B123" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="C123" t="s">
         <v>91</v>
       </c>
       <c r="D123" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E123" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F123" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="G123" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H123" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I123" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J123">
         <v>2</v>
@@ -7866,18 +7920,18 @@
         <v>21</v>
       </c>
       <c r="L123">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M123" t="s">
         <v>22</v>
       </c>
       <c r="N123" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B124" t="s">
         <v>181</v>
@@ -7886,19 +7940,19 @@
         <v>91</v>
       </c>
       <c r="D124" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E124" t="s">
-        <v>198</v>
+        <v>363</v>
       </c>
       <c r="F124" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G124" t="s">
-        <v>198</v>
+        <v>363</v>
       </c>
       <c r="H124" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I124" t="s">
         <v>559</v>
@@ -7921,7 +7975,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B125" t="s">
         <v>181</v>
@@ -7930,22 +7984,22 @@
         <v>91</v>
       </c>
       <c r="D125" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E125" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F125" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G125" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H125" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I125" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J125">
         <v>2</v>
@@ -7965,122 +8019,122 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B126" t="s">
-        <v>181</v>
+        <v>565</v>
       </c>
       <c r="C126" t="s">
-        <v>91</v>
+        <v>566</v>
       </c>
       <c r="D126" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E126" t="s">
-        <v>366</v>
+        <v>568</v>
       </c>
       <c r="F126" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G126" t="s">
-        <v>366</v>
+        <v>568</v>
       </c>
       <c r="H126" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="I126" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K126" t="s">
         <v>21</v>
       </c>
       <c r="L126">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M126" t="s">
         <v>22</v>
       </c>
       <c r="N126" t="s">
-        <v>184</v>
+        <v>565</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B127" t="s">
-        <v>181</v>
+        <v>572</v>
       </c>
       <c r="C127" t="s">
-        <v>91</v>
+        <v>573</v>
       </c>
       <c r="D127" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="E127" t="s">
-        <v>366</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="G127" t="s">
-        <v>366</v>
+        <v>190</v>
       </c>
       <c r="H127" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="I127" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="J127">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K127" t="s">
         <v>21</v>
       </c>
       <c r="L127">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M127" t="s">
         <v>22</v>
       </c>
       <c r="N127" t="s">
-        <v>184</v>
+        <v>572</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B128" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="C128" t="s">
-        <v>569</v>
+        <v>447</v>
       </c>
       <c r="D128" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="E128" t="s">
-        <v>571</v>
+        <v>190</v>
       </c>
       <c r="F128" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="G128" t="s">
-        <v>571</v>
+        <v>190</v>
       </c>
       <c r="H128" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="I128" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="J128">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K128" t="s">
         <v>21</v>
@@ -8092,124 +8146,124 @@
         <v>22</v>
       </c>
       <c r="N128" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B129" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C129" t="s">
-        <v>576</v>
+        <v>339</v>
       </c>
       <c r="D129" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="E129" t="s">
         <v>190</v>
       </c>
       <c r="F129" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="G129" t="s">
         <v>190</v>
       </c>
       <c r="H129" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="I129" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="J129">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K129" t="s">
         <v>21</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M129" t="s">
         <v>22</v>
       </c>
       <c r="N129" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B130" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C130" t="s">
-        <v>449</v>
+        <v>588</v>
       </c>
       <c r="D130" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="E130" t="s">
-        <v>190</v>
+        <v>590</v>
       </c>
       <c r="F130" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="G130" t="s">
-        <v>190</v>
+        <v>590</v>
       </c>
       <c r="H130" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="I130" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="J130">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K130" t="s">
         <v>21</v>
       </c>
       <c r="L130">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M130" t="s">
         <v>22</v>
       </c>
       <c r="N130" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B131" t="s">
-        <v>586</v>
+        <v>24</v>
       </c>
       <c r="C131" t="s">
-        <v>338</v>
+        <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="E131" t="s">
-        <v>190</v>
+        <v>595</v>
       </c>
       <c r="F131" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="G131" t="s">
-        <v>190</v>
+        <v>595</v>
       </c>
       <c r="H131" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="I131" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="J131">
         <v>2</v>
@@ -8218,86 +8272,86 @@
         <v>21</v>
       </c>
       <c r="L131">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M131" t="s">
         <v>22</v>
       </c>
       <c r="N131" t="s">
-        <v>586</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B132" t="s">
-        <v>590</v>
+        <v>90</v>
       </c>
       <c r="C132" t="s">
-        <v>591</v>
+        <v>91</v>
       </c>
       <c r="D132" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E132" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F132" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="G132" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="H132" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="I132" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="J132">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K132" t="s">
         <v>21</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M132" t="s">
         <v>22</v>
       </c>
       <c r="N132" t="s">
-        <v>590</v>
+        <v>95</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B133" t="s">
-        <v>24</v>
+        <v>602</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="D133" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E133" t="s">
-        <v>319</v>
+        <v>604</v>
       </c>
       <c r="F133" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="G133" t="s">
-        <v>319</v>
+        <v>604</v>
       </c>
       <c r="H133" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="I133" t="s">
-        <v>319</v>
+        <v>606</v>
       </c>
       <c r="J133">
         <v>2</v>
@@ -8306,42 +8360,42 @@
         <v>21</v>
       </c>
       <c r="L133">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M133" t="s">
         <v>22</v>
       </c>
       <c r="N133" t="s">
-        <v>29</v>
+        <v>607</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="B134" t="s">
-        <v>90</v>
+        <v>327</v>
       </c>
       <c r="C134" t="s">
         <v>91</v>
       </c>
       <c r="D134" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="E134" t="s">
-        <v>601</v>
+        <v>232</v>
       </c>
       <c r="F134" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="G134" t="s">
-        <v>601</v>
+        <v>232</v>
       </c>
       <c r="H134" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="I134" t="s">
-        <v>601</v>
+        <v>232</v>
       </c>
       <c r="J134">
         <v>2</v>
@@ -8350,86 +8404,86 @@
         <v>21</v>
       </c>
       <c r="L134">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M134" t="s">
         <v>22</v>
       </c>
       <c r="N134" t="s">
-        <v>95</v>
+        <v>330</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B135" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C135" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="D135" t="s">
-        <v>605</v>
+        <v>197</v>
       </c>
       <c r="E135" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F135" t="s">
-        <v>605</v>
+        <v>197</v>
       </c>
       <c r="G135" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="H135" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="I135" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="J135">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K135" t="s">
         <v>21</v>
       </c>
       <c r="L135">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M135" t="s">
         <v>22</v>
       </c>
       <c r="N135" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B136" t="s">
-        <v>326</v>
+        <v>24</v>
       </c>
       <c r="C136" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E136" t="s">
-        <v>232</v>
+        <v>618</v>
       </c>
       <c r="F136" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="G136" t="s">
-        <v>232</v>
+        <v>618</v>
       </c>
       <c r="H136" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="I136" t="s">
-        <v>232</v>
+        <v>619</v>
       </c>
       <c r="J136">
         <v>2</v>
@@ -8438,89 +8492,89 @@
         <v>21</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M136" t="s">
         <v>22</v>
       </c>
       <c r="N136" t="s">
-        <v>329</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B137" t="s">
-        <v>614</v>
+        <v>24</v>
       </c>
       <c r="C137" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="E137" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F137" t="s">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="G137" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H137" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="I137" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="J137">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K137" t="s">
         <v>21</v>
       </c>
       <c r="L137">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M137" t="s">
         <v>22</v>
       </c>
       <c r="N137" t="s">
-        <v>614</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>625</v>
       </c>
       <c r="D138" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="E138" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="F138" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="G138" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="H138" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="I138" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="J138">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K138" t="s">
         <v>21</v>
@@ -8532,36 +8586,36 @@
         <v>22</v>
       </c>
       <c r="N138" t="s">
-        <v>29</v>
+        <v>624</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B139" t="s">
-        <v>24</v>
+        <v>631</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>632</v>
       </c>
       <c r="D139" t="s">
-        <v>74</v>
+        <v>633</v>
       </c>
       <c r="E139" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="F139" t="s">
-        <v>74</v>
+        <v>633</v>
       </c>
       <c r="G139" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="H139" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="I139" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="J139">
         <v>2</v>
@@ -8576,80 +8630,80 @@
         <v>22</v>
       </c>
       <c r="N139" t="s">
-        <v>29</v>
+        <v>636</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="B140" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C140" t="s">
-        <v>627</v>
+        <v>203</v>
       </c>
       <c r="D140" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="E140" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="F140" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="G140" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="H140" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="I140" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="J140">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K140" t="s">
         <v>21</v>
       </c>
       <c r="L140">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M140" t="s">
         <v>22</v>
       </c>
       <c r="N140" t="s">
-        <v>626</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="B141" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C141" t="s">
-        <v>634</v>
+        <v>203</v>
       </c>
       <c r="D141" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="E141" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F141" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="G141" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H141" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="I141" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="J141">
         <v>2</v>
@@ -8658,42 +8712,42 @@
         <v>21</v>
       </c>
       <c r="L141">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M141" t="s">
         <v>22</v>
       </c>
       <c r="N141" t="s">
-        <v>638</v>
+        <v>206</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B142" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C142" t="s">
         <v>203</v>
       </c>
       <c r="D142" t="s">
+        <v>645</v>
+      </c>
+      <c r="E142" t="s">
+        <v>640</v>
+      </c>
+      <c r="F142" t="s">
+        <v>645</v>
+      </c>
+      <c r="G142" t="s">
+        <v>640</v>
+      </c>
+      <c r="H142" t="s">
+        <v>645</v>
+      </c>
+      <c r="I142" t="s">
         <v>641</v>
-      </c>
-      <c r="E142" t="s">
-        <v>642</v>
-      </c>
-      <c r="F142" t="s">
-        <v>641</v>
-      </c>
-      <c r="G142" t="s">
-        <v>642</v>
-      </c>
-      <c r="H142" t="s">
-        <v>641</v>
-      </c>
-      <c r="I142" t="s">
-        <v>643</v>
       </c>
       <c r="J142">
         <v>2</v>
@@ -8713,31 +8767,31 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B143" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C143" t="s">
         <v>203</v>
       </c>
       <c r="D143" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E143" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F143" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G143" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H143" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="I143" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="J143">
         <v>2</v>
@@ -8757,31 +8811,31 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B144" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C144" t="s">
         <v>203</v>
       </c>
       <c r="D144" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E144" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F144" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G144" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H144" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I144" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="J144">
         <v>2</v>
@@ -8801,31 +8855,31 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B145" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C145" t="s">
         <v>203</v>
       </c>
       <c r="D145" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E145" t="s">
-        <v>642</v>
+        <v>224</v>
       </c>
       <c r="F145" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G145" t="s">
-        <v>642</v>
+        <v>224</v>
       </c>
       <c r="H145" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I145" t="s">
-        <v>643</v>
+        <v>224</v>
       </c>
       <c r="J145">
         <v>2</v>
@@ -8834,7 +8888,7 @@
         <v>21</v>
       </c>
       <c r="L145">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M145" t="s">
         <v>22</v>
@@ -8845,31 +8899,31 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B146" t="s">
-        <v>640</v>
+        <v>361</v>
       </c>
       <c r="C146" t="s">
         <v>203</v>
       </c>
       <c r="D146" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E146" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="F146" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="G146" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="H146" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="I146" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="J146">
         <v>2</v>
@@ -8884,36 +8938,36 @@
         <v>22</v>
       </c>
       <c r="N146" t="s">
-        <v>206</v>
+        <v>365</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B147" t="s">
-        <v>640</v>
+        <v>361</v>
       </c>
       <c r="C147" t="s">
         <v>203</v>
       </c>
       <c r="D147" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="E147" t="s">
-        <v>224</v>
+        <v>655</v>
       </c>
       <c r="F147" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="G147" t="s">
-        <v>224</v>
+        <v>655</v>
       </c>
       <c r="H147" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="I147" t="s">
-        <v>224</v>
+        <v>656</v>
       </c>
       <c r="J147">
         <v>2</v>
@@ -8922,45 +8976,45 @@
         <v>21</v>
       </c>
       <c r="L147">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M147" t="s">
         <v>22</v>
       </c>
       <c r="N147" t="s">
-        <v>206</v>
+        <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B148" t="s">
-        <v>364</v>
+        <v>660</v>
       </c>
       <c r="C148" t="s">
-        <v>203</v>
+        <v>661</v>
       </c>
       <c r="D148" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="E148" t="s">
-        <v>657</v>
+        <v>75</v>
       </c>
       <c r="F148" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G148" t="s">
-        <v>657</v>
+        <v>75</v>
       </c>
       <c r="H148" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="I148" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K148" t="s">
         <v>21</v>
@@ -8972,80 +9026,80 @@
         <v>22</v>
       </c>
       <c r="N148" t="s">
-        <v>368</v>
+        <v>660</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B149" t="s">
-        <v>364</v>
+        <v>660</v>
       </c>
       <c r="C149" t="s">
-        <v>203</v>
+        <v>661</v>
       </c>
       <c r="D149" t="s">
+        <v>78</v>
+      </c>
+      <c r="E149" t="s">
+        <v>102</v>
+      </c>
+      <c r="F149" t="s">
+        <v>78</v>
+      </c>
+      <c r="G149" t="s">
+        <v>102</v>
+      </c>
+      <c r="H149" t="s">
+        <v>666</v>
+      </c>
+      <c r="I149" t="s">
+        <v>667</v>
+      </c>
+      <c r="J149">
+        <v>4</v>
+      </c>
+      <c r="K149" t="s">
+        <v>21</v>
+      </c>
+      <c r="L149">
+        <v>180</v>
+      </c>
+      <c r="M149" t="s">
+        <v>22</v>
+      </c>
+      <c r="N149" t="s">
         <v>660</v>
-      </c>
-      <c r="E149" t="s">
-        <v>657</v>
-      </c>
-      <c r="F149" t="s">
-        <v>660</v>
-      </c>
-      <c r="G149" t="s">
-        <v>657</v>
-      </c>
-      <c r="H149" t="s">
-        <v>660</v>
-      </c>
-      <c r="I149" t="s">
-        <v>658</v>
-      </c>
-      <c r="J149">
-        <v>2</v>
-      </c>
-      <c r="K149" t="s">
-        <v>21</v>
-      </c>
-      <c r="L149">
-        <v>270</v>
-      </c>
-      <c r="M149" t="s">
-        <v>22</v>
-      </c>
-      <c r="N149" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>668</v>
+      </c>
+      <c r="B150" t="s">
+        <v>660</v>
+      </c>
+      <c r="C150" t="s">
         <v>661</v>
       </c>
-      <c r="B150" t="s">
-        <v>662</v>
-      </c>
-      <c r="C150" t="s">
-        <v>663</v>
-      </c>
       <c r="D150" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E150" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F150" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="G150" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="H150" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I150" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="J150">
         <v>4</v>
@@ -9054,42 +9108,42 @@
         <v>21</v>
       </c>
       <c r="L150">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M150" t="s">
         <v>22</v>
       </c>
       <c r="N150" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B151" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C151" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D151" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E151" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F151" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="G151" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="H151" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="I151" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="J151">
         <v>4</v>
@@ -9104,36 +9158,36 @@
         <v>22</v>
       </c>
       <c r="N151" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B152" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C152" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D152" t="s">
-        <v>649</v>
+        <v>70</v>
       </c>
       <c r="E152" t="s">
-        <v>106</v>
+        <v>618</v>
       </c>
       <c r="F152" t="s">
-        <v>649</v>
+        <v>70</v>
       </c>
       <c r="G152" t="s">
-        <v>106</v>
+        <v>618</v>
       </c>
       <c r="H152" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I152" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="J152">
         <v>4</v>
@@ -9142,42 +9196,42 @@
         <v>21</v>
       </c>
       <c r="L152">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M152" t="s">
         <v>22</v>
       </c>
       <c r="N152" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B153" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C153" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D153" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E153" t="s">
-        <v>62</v>
+        <v>678</v>
       </c>
       <c r="F153" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G153" t="s">
-        <v>62</v>
+        <v>678</v>
       </c>
       <c r="H153" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="I153" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="J153">
         <v>4</v>
@@ -9192,124 +9246,124 @@
         <v>22</v>
       </c>
       <c r="N153" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B154" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="C154" t="s">
-        <v>663</v>
+        <v>91</v>
       </c>
       <c r="D154" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E154" t="s">
-        <v>620</v>
+        <v>66</v>
       </c>
       <c r="F154" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="G154" t="s">
-        <v>620</v>
+        <v>66</v>
       </c>
       <c r="H154" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="I154" t="s">
-        <v>678</v>
+        <v>66</v>
       </c>
       <c r="J154">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K154" t="s">
         <v>21</v>
       </c>
       <c r="L154">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M154" t="s">
         <v>22</v>
       </c>
       <c r="N154" t="s">
-        <v>662</v>
+        <v>684</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B155" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="C155" t="s">
-        <v>663</v>
+        <v>91</v>
       </c>
       <c r="D155" t="s">
-        <v>74</v>
+        <v>686</v>
       </c>
       <c r="E155" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F155" t="s">
-        <v>74</v>
+        <v>686</v>
       </c>
       <c r="G155" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H155" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="I155" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="J155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K155" t="s">
         <v>21</v>
       </c>
       <c r="L155">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M155" t="s">
         <v>22</v>
       </c>
       <c r="N155" t="s">
-        <v>662</v>
+        <v>684</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B156" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C156" t="s">
         <v>91</v>
       </c>
       <c r="D156" t="s">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="E156" t="s">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="F156" t="s">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="G156" t="s">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="H156" t="s">
-        <v>685</v>
+        <v>323</v>
       </c>
       <c r="I156" t="s">
-        <v>66</v>
+        <v>287</v>
       </c>
       <c r="J156">
         <v>2</v>
@@ -9318,42 +9372,42 @@
         <v>21</v>
       </c>
       <c r="L156">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M156" t="s">
         <v>22</v>
       </c>
       <c r="N156" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B157" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C157" t="s">
         <v>91</v>
       </c>
       <c r="D157" t="s">
-        <v>688</v>
+        <v>323</v>
       </c>
       <c r="E157" t="s">
-        <v>680</v>
+        <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>688</v>
+        <v>323</v>
       </c>
       <c r="G157" t="s">
-        <v>680</v>
+        <v>318</v>
       </c>
       <c r="H157" t="s">
-        <v>688</v>
+        <v>323</v>
       </c>
       <c r="I157" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="J157">
         <v>2</v>
@@ -9368,7 +9422,183 @@
         <v>22</v>
       </c>
       <c r="N157" t="s">
-        <v>686</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>693</v>
+      </c>
+      <c r="B158" t="s">
+        <v>141</v>
+      </c>
+      <c r="C158" t="s">
+        <v>91</v>
+      </c>
+      <c r="D158" t="s">
+        <v>694</v>
+      </c>
+      <c r="E158" t="s">
+        <v>363</v>
+      </c>
+      <c r="F158" t="s">
+        <v>694</v>
+      </c>
+      <c r="G158" t="s">
+        <v>363</v>
+      </c>
+      <c r="H158" t="s">
+        <v>694</v>
+      </c>
+      <c r="I158" t="s">
+        <v>553</v>
+      </c>
+      <c r="J158">
+        <v>2</v>
+      </c>
+      <c r="K158" t="s">
+        <v>21</v>
+      </c>
+      <c r="L158">
+        <v>90</v>
+      </c>
+      <c r="M158" t="s">
+        <v>22</v>
+      </c>
+      <c r="N158" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>695</v>
+      </c>
+      <c r="B159" t="s">
+        <v>345</v>
+      </c>
+      <c r="C159" t="s">
+        <v>346</v>
+      </c>
+      <c r="D159" t="s">
+        <v>334</v>
+      </c>
+      <c r="E159" t="s">
+        <v>696</v>
+      </c>
+      <c r="F159" t="s">
+        <v>334</v>
+      </c>
+      <c r="G159" t="s">
+        <v>696</v>
+      </c>
+      <c r="H159" t="s">
+        <v>697</v>
+      </c>
+      <c r="I159" t="s">
+        <v>698</v>
+      </c>
+      <c r="J159">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>21</v>
+      </c>
+      <c r="L159">
+        <v>90</v>
+      </c>
+      <c r="M159" t="s">
+        <v>22</v>
+      </c>
+      <c r="N159" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>699</v>
+      </c>
+      <c r="B160" t="s">
+        <v>141</v>
+      </c>
+      <c r="C160" t="s">
+        <v>91</v>
+      </c>
+      <c r="D160" t="s">
+        <v>700</v>
+      </c>
+      <c r="E160" t="s">
+        <v>701</v>
+      </c>
+      <c r="F160" t="s">
+        <v>700</v>
+      </c>
+      <c r="G160" t="s">
+        <v>701</v>
+      </c>
+      <c r="H160" t="s">
+        <v>702</v>
+      </c>
+      <c r="I160" t="s">
+        <v>703</v>
+      </c>
+      <c r="J160">
+        <v>2</v>
+      </c>
+      <c r="K160" t="s">
+        <v>21</v>
+      </c>
+      <c r="L160">
+        <v>45</v>
+      </c>
+      <c r="M160" t="s">
+        <v>22</v>
+      </c>
+      <c r="N160" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>704</v>
+      </c>
+      <c r="B161" t="s">
+        <v>421</v>
+      </c>
+      <c r="C161" t="s">
+        <v>422</v>
+      </c>
+      <c r="D161" t="s">
+        <v>705</v>
+      </c>
+      <c r="E161" t="s">
+        <v>424</v>
+      </c>
+      <c r="F161" t="s">
+        <v>706</v>
+      </c>
+      <c r="G161" t="s">
+        <v>424</v>
+      </c>
+      <c r="H161" t="s">
+        <v>707</v>
+      </c>
+      <c r="I161" t="s">
+        <v>427</v>
+      </c>
+      <c r="J161">
+        <v>23</v>
+      </c>
+      <c r="K161" t="s">
+        <v>21</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161" t="s">
+        <v>88</v>
+      </c>
+      <c r="N161" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
